--- a/data/trans_dic/P55$familiarvive-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 23,87</t>
+          <t>10,76; 24,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 26,5</t>
+          <t>10,82; 26,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 24,96</t>
+          <t>10,21; 24,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 13,92</t>
+          <t>5,02; 14,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,58; 39,47</t>
+          <t>26,16; 39,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,65; 35,54</t>
+          <t>23,56; 35,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,91; 35,16</t>
+          <t>21,15; 35,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 24,72</t>
+          <t>17,31; 24,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 32,36</t>
+          <t>21,75; 32,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 30,58</t>
+          <t>21,22; 30,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,85; 30,21</t>
+          <t>19,7; 30,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 20,57</t>
+          <t>14,89; 20,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,8</t>
+          <t>0,0; 27,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 45,42</t>
+          <t>5,25; 44,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 35,9</t>
+          <t>3,29; 31,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 24,53</t>
+          <t>7,0; 23,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 58,76</t>
+          <t>7,74; 56,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 49,9</t>
+          <t>9,88; 51,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 39,76</t>
+          <t>11,45; 37,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 21,29</t>
+          <t>8,0; 20,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 34,88</t>
+          <t>4,28; 35,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 38,76</t>
+          <t>12,24; 41,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 31,3</t>
+          <t>11,71; 32,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,57</t>
+          <t>9,51; 20,15</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,22</t>
+          <t>0,0; 65,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,75</t>
+          <t>0,0; 32,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 50,1</t>
+          <t>15,65; 51,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,33</t>
+          <t>0,0; 37,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,52</t>
+          <t>0,0; 66,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 34,32</t>
+          <t>10,41; 34,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 22,41</t>
+          <t>9,94; 22,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,09</t>
+          <t>11,84; 25,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,32</t>
+          <t>9,96; 22,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 14,99</t>
+          <t>6,99; 15,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,77; 37,24</t>
+          <t>24,37; 37,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,5; 35,06</t>
+          <t>24,07; 35,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 33,14</t>
+          <t>20,8; 32,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 23,0</t>
+          <t>17,21; 23,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,76; 29,66</t>
+          <t>20,75; 30,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,14; 30,09</t>
+          <t>20,75; 29,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,0; 28,01</t>
+          <t>18,81; 27,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 19,57</t>
+          <t>14,39; 19,73</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10742; 24594</t>
+          <t>11084; 25294</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13857; 32899</t>
+          <t>13428; 33410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9820; 23329</t>
+          <t>9547; 23306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4474; 13595</t>
+          <t>4903; 13835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52666; 81244</t>
+          <t>53857; 80833</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59324; 89158</t>
+          <t>59102; 88092</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45697; 73339</t>
+          <t>44117; 73861</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44735; 63708</t>
+          <t>44606; 63614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>68032; 99947</t>
+          <t>67193; 100408</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79113; 114675</t>
+          <t>79573; 116026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59957; 91246</t>
+          <t>59488; 90850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52687; 73085</t>
+          <t>52902; 74366</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4796</t>
+          <t>0; 3954</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1041; 9091</t>
+          <t>1050; 9004</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>755; 8212</t>
+          <t>752; 7287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2943; 10554</t>
+          <t>3009; 9928</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1024; 7932</t>
+          <t>1045; 7592</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1978; 10555</t>
+          <t>2090; 10938</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6021; 20693</t>
+          <t>5961; 19708</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4551; 11636</t>
+          <t>4371; 11473</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1230; 9656</t>
+          <t>1184; 9807</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4548; 15957</t>
+          <t>5037; 16919</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8362; 23447</t>
+          <t>8774; 24494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9306; 19119</t>
+          <t>9288; 19687</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6482</t>
+          <t>0; 6165</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5103</t>
+          <t>0; 4889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1938; 7008</t>
+          <t>2190; 7196</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7607</t>
+          <t>0; 7799</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4292</t>
+          <t>0; 4300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3046; 9988</t>
+          <t>3029; 10118</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12488; 28367</t>
+          <t>12583; 28630</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17908; 38132</t>
+          <t>17303; 37958</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11466; 25897</t>
+          <t>12101; 26920</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10570; 23360</t>
+          <t>10890; 23931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>57205; 85990</t>
+          <t>56279; 85605</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64946; 96909</t>
+          <t>66540; 96887</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55186; 88615</t>
+          <t>55599; 86891</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55345; 75064</t>
+          <t>56163; 77168</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74219; 106044</t>
+          <t>74176; 108128</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89336; 127161</t>
+          <t>87682; 126082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70004; 108901</t>
+          <t>73146; 108127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70435; 94364</t>
+          <t>69380; 95145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiarvive-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiarvive-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 24,55</t>
+          <t>10,18; 24,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 26,92</t>
+          <t>11,57; 28,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,21; 24,94</t>
+          <t>10,42; 25,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,17</t>
+          <t>4,86; 14,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,16; 39,27</t>
+          <t>26,08; 39,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,56; 35,12</t>
+          <t>24,19; 36,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 35,41</t>
+          <t>21,94; 36,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 24,69</t>
+          <t>17,16; 25,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,75; 32,51</t>
+          <t>22,5; 32,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 30,94</t>
+          <t>21,2; 30,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 30,08</t>
+          <t>19,55; 30,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,89; 20,93</t>
+          <t>14,59; 20,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,87</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 44,99</t>
+          <t>5,12; 44,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 31,85</t>
+          <t>3,38; 33,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 23,08</t>
+          <t>7,81; 24,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 56,24</t>
+          <t>7,8; 56,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 51,71</t>
+          <t>9,91; 51,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 37,87</t>
+          <t>10,82; 36,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 20,99</t>
+          <t>9,12; 21,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 35,42</t>
+          <t>4,12; 35,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 41,1</t>
+          <t>11,96; 39,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 32,69</t>
+          <t>11,18; 31,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,15</t>
+          <t>9,86; 20,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,83</t>
+          <t>0,0; 65,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,34</t>
+          <t>0,0; 28,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 51,45</t>
+          <t>13,67; 47,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,25</t>
+          <t>0,0; 35,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,65</t>
+          <t>0,0; 66,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,41; 34,76</t>
+          <t>10,08; 31,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 22,62</t>
+          <t>9,86; 22,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 25,97</t>
+          <t>12,08; 26,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,16</t>
+          <t>9,5; 21,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,36</t>
+          <t>7,04; 15,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,37; 37,07</t>
+          <t>24,39; 36,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 35,05</t>
+          <t>23,67; 35,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 32,5</t>
+          <t>21,34; 33,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 23,65</t>
+          <t>17,16; 23,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,75; 30,25</t>
+          <t>20,76; 30,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,75; 29,84</t>
+          <t>21,05; 30,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 27,81</t>
+          <t>18,6; 27,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 19,73</t>
+          <t>14,55; 19,77</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53497</t>
+          <t>57859</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62119</t>
+          <t>66670</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11084; 25294</t>
+          <t>10486; 24820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13428; 33410</t>
+          <t>14362; 35866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9547; 23306</t>
+          <t>9735; 23510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4903; 13835</t>
+          <t>5048; 14851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53857; 80833</t>
+          <t>53682; 81517</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59102; 88092</t>
+          <t>60672; 90932</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44117; 73861</t>
+          <t>45769; 75291</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44606; 63614</t>
+          <t>47502; 69947</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67193; 100408</t>
+          <t>69506; 99954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79573; 116026</t>
+          <t>79502; 115711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59488; 90850</t>
+          <t>59060; 91068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52902; 74366</t>
+          <t>55525; 79118</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>16212</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 3927</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1050; 9004</t>
+          <t>1026; 8986</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>752; 7287</t>
+          <t>773; 7610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3009; 9928</t>
+          <t>3696; 11826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1045; 7592</t>
+          <t>1052; 7592</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2090; 10938</t>
+          <t>2097; 10804</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5961; 19708</t>
+          <t>5633; 19055</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4371; 11473</t>
+          <t>5716; 13690</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1184; 9807</t>
+          <t>1140; 9956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5037; 16919</t>
+          <t>4923; 16351</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8774; 24494</t>
+          <t>8372; 23748</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9288; 19687</t>
+          <t>10844; 22962</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5986</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6165</t>
+          <t>0; 6109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2190; 7196</t>
+          <t>2152; 7401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 7799</t>
+          <t>0; 7414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4300</t>
+          <t>0; 4291</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3029; 10118</t>
+          <t>3257; 10242</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65078</t>
+          <t>71251</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>88867</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12583; 28630</t>
+          <t>12479; 28676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17303; 37958</t>
+          <t>17651; 38661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12101; 26920</t>
+          <t>11535; 26314</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10890; 23931</t>
+          <t>11797; 25317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56279; 85605</t>
+          <t>56317; 84259</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66540; 96887</t>
+          <t>65421; 98173</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55599; 86891</t>
+          <t>57053; 88563</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56163; 77168</t>
+          <t>60939; 83984</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74176; 108128</t>
+          <t>74223; 108590</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87682; 126082</t>
+          <t>88940; 127224</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73146; 108127</t>
+          <t>72307; 107990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69380; 95145</t>
+          <t>76103; 103349</t>
         </is>
       </c>
     </row>
